--- a/PARADISE_WP1_afvinklijst.xlsx
+++ b/PARADISE_WP1_afvinklijst.xlsx
@@ -4280,8 +4280,8 @@
   <mergeCells count="11">
     <mergeCell ref="A65:I65"/>
     <mergeCell ref="A73:I73"/>
+    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A60:I60"/>
     <mergeCell ref="A1:I1"/>
@@ -4323,7 +4323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="14" min="1" max="1"/>
@@ -5527,6 +5527,105 @@
       <c r="G43" s="23" t="inlineStr">
         <is>
           <t>Uitgezocht 11 sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" s="14">
+      <c r="A44" s="26" t="n"/>
+      <c r="B44" s="23" t="inlineStr">
+        <is>
+          <t>eCRF 24: koptekst van deel A2 zegt 'Appendix 23'</t>
+        </is>
+      </c>
+      <c r="C44" s="23" t="inlineStr">
+        <is>
+          <t>Deel A1 is getiteld Appendix 24, deel A2 Appendix 23. Een van de twee is fout; de bestandsnaam en het register zeggen 24.</t>
+        </is>
+      </c>
+      <c r="D44" s="23" t="inlineStr">
+        <is>
+          <t>eCRF 24</t>
+        </is>
+      </c>
+      <c r="E44" s="23" t="inlineStr">
+        <is>
+          <t>Laag</t>
+        </is>
+      </c>
+      <c r="F44" s="23" t="inlineStr">
+        <is>
+          <t>Te doen</t>
+        </is>
+      </c>
+      <c r="G44" s="23" t="inlineStr">
+        <is>
+          <t>Vastgesteld 13 sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" s="14">
+      <c r="A45" s="26" t="n"/>
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t>Doelregio's op maand 6, 12 en 18</t>
+        </is>
+      </c>
+      <c r="C45" s="23" t="inlineStr">
+        <is>
+          <t>eCRF 24 is opgesteld voor visite 2 en zegt telkens 'definieer de drie doelregio's', zonder te vermelden of ze op de latere meetmomenten worden overgenomen. Voor het volgen van het ontlastende effect over de tijd zouden ze dezelfde moeten blijven.</t>
+        </is>
+      </c>
+      <c r="D45" s="23" t="inlineStr">
+        <is>
+          <t>eCRF 24, SAP</t>
+        </is>
+      </c>
+      <c r="E45" s="23" t="inlineStr">
+        <is>
+          <t>Hoog</t>
+        </is>
+      </c>
+      <c r="F45" s="23" t="inlineStr">
+        <is>
+          <t>Te doen</t>
+        </is>
+      </c>
+      <c r="G45" s="23" t="inlineStr">
+        <is>
+          <t>Vastgesteld 13 sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" s="14">
+      <c r="A46" s="26" t="n"/>
+      <c r="B46" s="23" t="inlineStr">
+        <is>
+          <t>Deelnemer met maar één paar schoeisel</t>
+        </is>
+      </c>
+      <c r="C46" s="23" t="inlineStr">
+        <is>
+          <t>eCRF 24 voorziet deel A1 (buitenschoeisel) en deel A2 (binnenschoeisel), elk met een volledige meetreeks. Vastleggen of deel A2 leeg blijft of vervalt als er maar één paar is.</t>
+        </is>
+      </c>
+      <c r="D46" s="23" t="inlineStr">
+        <is>
+          <t>eCRF 24, SOP 09b</t>
+        </is>
+      </c>
+      <c r="E46" s="23" t="inlineStr">
+        <is>
+          <t>Middel</t>
+        </is>
+      </c>
+      <c r="F46" s="23" t="inlineStr">
+        <is>
+          <t>Te doen</t>
+        </is>
+      </c>
+      <c r="G46" s="23" t="inlineStr">
+        <is>
+          <t>Vastgesteld 13 sep</t>
         </is>
       </c>
     </row>
@@ -5554,7 +5653,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F29 F38:F43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F29 F38:F43 F44:F46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Te doen,Bezig,Klaar,Geblokkeerd,Vervalt"</formula1>
     </dataValidation>
   </dataValidations>

--- a/PARADISE_WP1_afvinklijst.xlsx
+++ b/PARADISE_WP1_afvinklijst.xlsx
@@ -4279,8 +4279,8 @@
   <autoFilter ref="A4:I79"/>
   <mergeCells count="11">
     <mergeCell ref="A65:I65"/>
+    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A73:I73"/>
-    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A60:I60"/>
@@ -4323,7 +4323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="14" min="1" max="1"/>
@@ -4349,6 +4349,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26.1" customHeight="1" s="14">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -4995,6 +4996,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="25" t="inlineStr">
         <is>
@@ -5336,12 +5338,12 @@
       <c r="A38" s="26" t="n"/>
       <c r="B38" s="23" t="inlineStr">
         <is>
-          <t>Novel database aanmaken</t>
+          <t>Novel database: route en beheer</t>
         </is>
       </c>
       <c r="C38" s="23" t="inlineStr">
         <is>
-          <t>De suite novel scientific 29.3.25 staat geïnstalleerd op de onderzoekslaptop (C:\novel, met SQL Server Express 2019), maar er is nog geen database: geen deelnemers, geen pedar-bestanden. Beslissen of er één centrale database komt of één per centrum.</t>
+          <t>De database bestaat sinds 14 september onder de naam Sint_Jan_Paradise_Project, met een testpersoon erin. Wat nog niet vastligt: of de klinieken rechtstreeks vanuit de database meten dan wel in novel studio, of er een centrale database komt of een per centrum, en hoe de vijf andere centra erin terechtkomen.</t>
         </is>
       </c>
       <c r="D38" s="23" t="inlineStr">
@@ -5361,7 +5363,7 @@
       </c>
       <c r="G38" s="23" t="inlineStr">
         <is>
-          <t>Openstaand punt 29</t>
+          <t>Aangemaakt 14 sep; route nog open</t>
         </is>
       </c>
     </row>
@@ -5626,6 +5628,105 @@
       <c r="G46" s="23" t="inlineStr">
         <is>
           <t>Vastgesteld 13 sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" s="14">
+      <c r="A47" s="26" t="n"/>
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t>Date of birth in de database</t>
+        </is>
+      </c>
+      <c r="C47" s="23" t="inlineStr">
+        <is>
+          <t>Novel vraagt een geboortedatum in het veld Persons. Samen met een centrum en een meetdatum is dat herleidbaar. Beslissen: alleen het geboortejaar, of het veld leeg laten.</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="inlineStr">
+        <is>
+          <t>novel database, DMP</t>
+        </is>
+      </c>
+      <c r="E47" s="23" t="inlineStr">
+        <is>
+          <t>Hoog</t>
+        </is>
+      </c>
+      <c r="F47" s="23" t="inlineStr">
+        <is>
+          <t>Te doen</t>
+        </is>
+      </c>
+      <c r="G47" s="23" t="inlineStr">
+        <is>
+          <t>GDPR — vastgesteld 14 sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" s="14">
+      <c r="A48" s="26" t="n"/>
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t>Map Manuals buiten de repo gehouden</t>
+        </is>
+      </c>
+      <c r="C48" s="23" t="inlineStr">
+        <is>
+          <t>KU Leuven License Cloud.pdf bevat de registratiecode voor cloud.orthotimer.com. De map staat nu in .gitignore zodat ze niet naar Netlify gepubliceerd wordt.</t>
+        </is>
+      </c>
+      <c r="D48" s="23" t="inlineStr">
+        <is>
+          <t>.gitignore</t>
+        </is>
+      </c>
+      <c r="E48" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="23" t="inlineStr">
+        <is>
+          <t>Klaar</t>
+        </is>
+      </c>
+      <c r="G48" s="23" t="inlineStr">
+        <is>
+          <t>14 sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" s="14">
+      <c r="A49" s="26" t="n"/>
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t>Verkeerde configuratie gezien op een echt scherm</t>
+        </is>
+      </c>
+      <c r="C49" s="23" t="inlineStr">
+        <is>
+          <t>Op de schermafbeelding van 14 september staat toestel plidar-G009L met een configuratie van plidar-G026: de linkerzender met de rechterconfiguratie. De software waarschuwt niet. Staat nu als figuur in de SOP.</t>
+        </is>
+      </c>
+      <c r="D49" s="23" t="inlineStr">
+        <is>
+          <t>SOP 09b</t>
+        </is>
+      </c>
+      <c r="E49" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="23" t="inlineStr">
+        <is>
+          <t>Klaar</t>
+        </is>
+      </c>
+      <c r="G49" s="23" t="inlineStr">
+        <is>
+          <t>Verwerkt in hoofdstuk 6</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5754,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F29 F38:F43 F44:F46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F29 F38:F43 F44:F46 F47:F49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Te doen,Bezig,Klaar,Geblokkeerd,Vervalt"</formula1>
     </dataValidation>
   </dataValidations>

--- a/PARADISE_WP1_afvinklijst.xlsx
+++ b/PARADISE_WP1_afvinklijst.xlsx
@@ -4279,9 +4279,9 @@
   <autoFilter ref="A4:I79"/>
   <mergeCells count="11">
     <mergeCell ref="A65:I65"/>
-    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A73:I73"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A60:I60"/>
     <mergeCell ref="A1:I1"/>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="C47" s="23" t="inlineStr">
         <is>
-          <t>Novel vraagt een geboortedatum in het veld Persons. Samen met een centrum en een meetdatum is dat herleidbaar. Beslissen: alleen het geboortejaar, of het veld leeg laten.</t>
+          <t>Beslist: 01/01/1900 voor elke deelnemer, samen met een X in beide naamvelden. Het afgeleide veld Age komt daardoor op 126 — dat maakt meteen zichtbaar dat het een plaatshouder is. De werkelijke leeftijd staat in de eCRF.</t>
         </is>
       </c>
       <c r="D47" s="23" t="inlineStr">
@@ -5650,17 +5650,17 @@
       </c>
       <c r="E47" s="23" t="inlineStr">
         <is>
-          <t>Hoog</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F47" s="23" t="inlineStr">
         <is>
-          <t>Te doen</t>
+          <t>Klaar</t>
         </is>
       </c>
       <c r="G47" s="23" t="inlineStr">
         <is>
-          <t>GDPR — vastgesteld 14 sep</t>
+          <t>Beslissing PI 14 sep</t>
         </is>
       </c>
     </row>

--- a/PARADISE_WP1_afvinklijst.xlsx
+++ b/PARADISE_WP1_afvinklijst.xlsx
@@ -4280,8 +4280,8 @@
   <mergeCells count="11">
     <mergeCell ref="A65:I65"/>
     <mergeCell ref="A73:I73"/>
+    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A60:I60"/>
     <mergeCell ref="A1:I1"/>
@@ -4323,7 +4323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="14" min="1" max="1"/>
@@ -5244,7 +5244,7 @@
       </c>
       <c r="C35" s="23" t="inlineStr">
         <is>
-          <t>Nagaan of MPP en MVP herberekend worden over de selectie, of dat alleen de grafiek inzoomt. Eén opname twee keer aflezen, volledig en met selectie</t>
+          <t>Beantwoord: Set Range past alleen de grafiek aan — begin, eind en verschuiven — en rekent niets opnieuw. De getallen blijven over de hele opname. Frames weglaten kan alleen achteraf, met file master in de novel database.</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
@@ -5254,17 +5254,17 @@
       </c>
       <c r="E35" s="23" t="inlineStr">
         <is>
-          <t>Middel</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="23" t="inlineStr">
         <is>
-          <t>Te doen</t>
+          <t>Klaar</t>
         </is>
       </c>
       <c r="G35" s="23" t="inlineStr">
         <is>
-          <t>Openstaand punt 28</t>
+          <t>Beslissing PI 14 sep</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="C45" s="23" t="inlineStr">
         <is>
-          <t>eCRF 24 is opgesteld voor visite 2 en zegt telkens 'definieer de drie doelregio's', zonder te vermelden of ze op de latere meetmomenten worden overgenomen. Voor het volgen van het ontlastende effect over de tijd zouden ze dezelfde moeten blijven.</t>
+          <t>Beantwoord: dezelfde drie regio's, over te nemen van het vorige formulier. Ze worden niet opnieuw gekozen.</t>
         </is>
       </c>
       <c r="D45" s="23" t="inlineStr">
@@ -5584,17 +5584,17 @@
       </c>
       <c r="E45" s="23" t="inlineStr">
         <is>
-          <t>Hoog</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F45" s="23" t="inlineStr">
         <is>
-          <t>Te doen</t>
+          <t>Klaar</t>
         </is>
       </c>
       <c r="G45" s="23" t="inlineStr">
         <is>
-          <t>Vastgesteld 13 sep</t>
+          <t>Beslissing PI 14 sep</t>
         </is>
       </c>
     </row>
@@ -5727,6 +5727,138 @@
       <c r="G49" s="23" t="inlineStr">
         <is>
           <t>Verwerkt in hoofdstuk 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" s="14">
+      <c r="A50" s="26" t="n"/>
+      <c r="B50" s="23" t="inlineStr">
+        <is>
+          <t>Batterij minstens 30%</t>
+        </is>
+      </c>
+      <c r="C50" s="23" t="inlineStr">
+        <is>
+          <t>Beslist: onder de 30% niet aan een meting beginnen. Staat nu in hoofdstuk 5 van de SOP en in de foutentabel.</t>
+        </is>
+      </c>
+      <c r="D50" s="23" t="inlineStr">
+        <is>
+          <t>SOP 09b</t>
+        </is>
+      </c>
+      <c r="E50" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="23" t="inlineStr">
+        <is>
+          <t>Klaar</t>
+        </is>
+      </c>
+      <c r="G50" s="23" t="inlineStr">
+        <is>
+          <t>Beslissing PI 14 sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" s="14">
+      <c r="A51" s="26" t="n"/>
+      <c r="B51" s="23" t="inlineStr">
+        <is>
+          <t>Route van de meetgegevens</t>
+        </is>
+      </c>
+      <c r="C51" s="23" t="inlineStr">
+        <is>
+          <t>Beslist: schermafbeelding in de Pressure Monitoring Tool plakken, opslaan, mailen naar janou.debusyer@kuleuven.be, en het bestand lokaal laten staan zodat het opgehaald kan worden als het mailen mislukt.</t>
+        </is>
+      </c>
+      <c r="D51" s="23" t="inlineStr">
+        <is>
+          <t>SOP 09b hfst. 12</t>
+        </is>
+      </c>
+      <c r="E51" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="23" t="inlineStr">
+        <is>
+          <t>Klaar</t>
+        </is>
+      </c>
+      <c r="G51" s="23" t="inlineStr">
+        <is>
+          <t>Beslissing PI 14 sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" s="14">
+      <c r="A52" s="26" t="n"/>
+      <c r="B52" s="23" t="inlineStr">
+        <is>
+          <t>E-mailadres in de SOP laten bevestigen</t>
+        </is>
+      </c>
+      <c r="C52" s="23" t="inlineStr">
+        <is>
+          <t>In de instructie staat janou.debusyer@kuleuven.be zoals doorgegeven. Dat wijkt af van de gebruikelijke schrijfwijze De Buyser → debuyser. Zes centra sturen hierop; één letter verkeerd betekent dat er niets aankomt.</t>
+        </is>
+      </c>
+      <c r="D52" s="23" t="inlineStr">
+        <is>
+          <t>SOP 09b hfst. 12</t>
+        </is>
+      </c>
+      <c r="E52" s="23" t="inlineStr">
+        <is>
+          <t>Hoog</t>
+        </is>
+      </c>
+      <c r="F52" s="23" t="inlineStr">
+        <is>
+          <t>Te doen</t>
+        </is>
+      </c>
+      <c r="G52" s="23" t="inlineStr">
+        <is>
+          <t>Te bevestigen</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" s="14">
+      <c r="A53" s="26" t="n"/>
+      <c r="B53" s="23" t="inlineStr">
+        <is>
+          <t>Pressure Monitoring Tool bijwerken</t>
+        </is>
+      </c>
+      <c r="C53" s="23" t="inlineStr">
+        <is>
+          <t>De tool rekent nog tegen een blootsvoetse baseline (kolommen Barefoot en % Change vs Barefoot) en kent zes regio's per voet in plaats van acht; de middenvoet is niet gesplitst en tenen 2-5 ontbreken. Er is alleen een blad Outdoor, terwijl eCRF 24 een deel A1 én A2 heeft.</t>
+        </is>
+      </c>
+      <c r="D53" s="23" t="inlineStr">
+        <is>
+          <t>Pressure monitoring tool_patient.xlsx</t>
+        </is>
+      </c>
+      <c r="E53" s="23" t="inlineStr">
+        <is>
+          <t>Hoog</t>
+        </is>
+      </c>
+      <c r="F53" s="23" t="inlineStr">
+        <is>
+          <t>Te doen</t>
+        </is>
+      </c>
+      <c r="G53" s="23" t="inlineStr">
+        <is>
+          <t>Vastgesteld 14 sep</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5886,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F29 F38:F43 F44:F46 F47:F49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F29 F38:F43 F44:F46 F47:F49 F50:F53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Te doen,Bezig,Klaar,Geblokkeerd,Vervalt"</formula1>
     </dataValidation>
   </dataValidations>

--- a/PARADISE_WP1_afvinklijst.xlsx
+++ b/PARADISE_WP1_afvinklijst.xlsx
@@ -4279,8 +4279,8 @@
   <autoFilter ref="A4:I79"/>
   <mergeCells count="11">
     <mergeCell ref="A65:I65"/>
+    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A73:I73"/>
-    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A60:I60"/>
@@ -4323,7 +4323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="14" min="1" max="1"/>
@@ -5800,12 +5800,12 @@
       <c r="A52" s="26" t="n"/>
       <c r="B52" s="23" t="inlineStr">
         <is>
-          <t>E-mailadres in de SOP laten bevestigen</t>
+          <t>E-mailadres bevestigd</t>
         </is>
       </c>
       <c r="C52" s="23" t="inlineStr">
         <is>
-          <t>In de instructie staat janou.debusyer@kuleuven.be zoals doorgegeven. Dat wijkt af van de gebruikelijke schrijfwijze De Buyser → debuyser. Zes centra sturen hierop; één letter verkeerd betekent dat er niets aankomt.</t>
+          <t>janou.debuyser@kuleuven.be — bevestigd op 14 september en aangepast in de SOP.</t>
         </is>
       </c>
       <c r="D52" s="23" t="inlineStr">
@@ -5815,17 +5815,17 @@
       </c>
       <c r="E52" s="23" t="inlineStr">
         <is>
-          <t>Hoog</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F52" s="23" t="inlineStr">
         <is>
-          <t>Te doen</t>
+          <t>Klaar</t>
         </is>
       </c>
       <c r="G52" s="23" t="inlineStr">
         <is>
-          <t>Te bevestigen</t>
+          <t>Bevestigd 14 sep</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C53" s="23" t="inlineStr">
         <is>
-          <t>De tool rekent nog tegen een blootsvoetse baseline (kolommen Barefoot en % Change vs Barefoot) en kent zes regio's per voet in plaats van acht; de middenvoet is niet gesplitst en tenen 2-5 ontbreken. Er is alleen een blad Outdoor, terwijl eCRF 24 een deel A1 én A2 heeft.</t>
+          <t>De tool kent zes regio's per voet in plaats van acht: de middenvoet is niet gesplitst in mediaal en lateraal en tenen 2-5 ontbreken. Dat raakt het samenvattingsblok én de twee blokken RAW DATA EXPORT, en dus ook het masker: dat moet zestien velden opleveren in plaats van twaalf. De kolomtitel 'Barefoot' is enkel een verkeerd label — bedoeld is de meting zonder aangepaste zool.</t>
         </is>
       </c>
       <c r="D53" s="23" t="inlineStr">
@@ -5857,6 +5857,39 @@
         </is>
       </c>
       <c r="G53" s="23" t="inlineStr">
+        <is>
+          <t>Nagekeken 14 sep; 8 regio's bevestigd</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" s="14">
+      <c r="A54" s="26" t="n"/>
+      <c r="B54" s="23" t="inlineStr">
+        <is>
+          <t>Twee regels die alleen in de tool staan</t>
+        </is>
+      </c>
+      <c r="C54" s="23" t="inlineStr">
+        <is>
+          <t>De doelregio's zijn per voet de twee plaatsen in de voorvoet of middenvoet met de hoogste piekdruk boven 200 kPa — de hiel telt niet mee. En de zool wordt ook aangepast als de piekdruk op een doelregio met 5% of meer gestegen is tegenover de vorige keer. Nagaan of die twee ook in het protocol en de SAP horen.</t>
+        </is>
+      </c>
+      <c r="D54" s="23" t="inlineStr">
+        <is>
+          <t>protocol, SAP, SOP 09b</t>
+        </is>
+      </c>
+      <c r="E54" s="23" t="inlineStr">
+        <is>
+          <t>Middel</t>
+        </is>
+      </c>
+      <c r="F54" s="23" t="inlineStr">
+        <is>
+          <t>Te doen</t>
+        </is>
+      </c>
+      <c r="G54" s="23" t="inlineStr">
         <is>
           <t>Vastgesteld 14 sep</t>
         </is>
@@ -5886,7 +5919,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F29 F38:F43 F44:F46 F47:F49 F50:F53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F29 F38:F43 F44:F46 F47:F49 F50:F53 F54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Te doen,Bezig,Klaar,Geblokkeerd,Vervalt"</formula1>
     </dataValidation>
   </dataValidations>

--- a/PARADISE_WP1_afvinklijst.xlsx
+++ b/PARADISE_WP1_afvinklijst.xlsx
@@ -4279,9 +4279,9 @@
   <autoFilter ref="A4:I79"/>
   <mergeCells count="11">
     <mergeCell ref="A65:I65"/>
-    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A73:I73"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A60:I60"/>
     <mergeCell ref="A1:I1"/>
@@ -4323,7 +4323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="14" min="1" max="1"/>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
-          <t>De blootsvoetse conditie vervalt; de twee overblijvende condities worden op elk meetmoment allebei gemeten</t>
+          <t>Gedaan op 14 september: de blootsvoetse conditie is uit het formulier, deel A1 (buitenschoeisel) is verwijderd, Tabel 3A heet weer Tabel 3. Wat nog moet: de regiotabellen van zes naar acht regio's per voet.</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="F30" s="23" t="inlineStr">
         <is>
-          <t>Te doen</t>
+          <t>Bezig</t>
         </is>
       </c>
       <c r="G30" s="23" t="inlineStr">
         <is>
-          <t>Volgt uit de beslissing</t>
+          <t>Deels gedaan 14 sep</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="C44" s="23" t="inlineStr">
         <is>
-          <t>Deel A1 is getiteld Appendix 24, deel A2 Appendix 23. Een van de twee is fout; de bestandsnaam en het register zeggen 24.</t>
+          <t>Vervalt: de dubbele titelregel stond op de pagina van deel A1, en dat deel is verwijderd.</t>
         </is>
       </c>
       <c r="D44" s="23" t="inlineStr">
@@ -5551,17 +5551,17 @@
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
-          <t>Laag</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F44" s="23" t="inlineStr">
         <is>
-          <t>Te doen</t>
+          <t>Klaar</t>
         </is>
       </c>
       <c r="G44" s="23" t="inlineStr">
         <is>
-          <t>Vastgesteld 13 sep</t>
+          <t>Beslissing PI 14 sep</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
       </c>
       <c r="C46" s="23" t="inlineStr">
         <is>
-          <t>eCRF 24 voorziet deel A1 (buitenschoeisel) en deel A2 (binnenschoeisel), elk met een volledige meetreeks. Vastleggen of deel A2 leeg blijft of vervalt als er maar één paar is.</t>
+          <t>Beantwoord: er wordt enkel in het binnenschoeisel gemeten. Deel A1 (buitenschoeisel) is uit eCRF 24 verwijderd; wat overblijft heet A. BINNENSCHOEISEL. Twee opnames per meetmoment, niet vier.</t>
         </is>
       </c>
       <c r="D46" s="23" t="inlineStr">
@@ -5617,17 +5617,17 @@
       </c>
       <c r="E46" s="23" t="inlineStr">
         <is>
-          <t>Middel</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F46" s="23" t="inlineStr">
         <is>
-          <t>Te doen</t>
+          <t>Klaar</t>
         </is>
       </c>
       <c r="G46" s="23" t="inlineStr">
         <is>
-          <t>Vastgesteld 13 sep</t>
+          <t>Beslissing PI 14 sep</t>
         </is>
       </c>
     </row>
@@ -5890,6 +5890,72 @@
         </is>
       </c>
       <c r="G54" s="23" t="inlineStr">
+        <is>
+          <t>Vastgesteld 14 sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" s="14">
+      <c r="A55" s="26" t="n"/>
+      <c r="B55" s="23" t="inlineStr">
+        <is>
+          <t>Tabblad hernoemd naar Visit</t>
+        </is>
+      </c>
+      <c r="C55" s="23" t="inlineStr">
+        <is>
+          <t>Het blad heette Outdoor, wat niet klopt nu er alleen in het binnenschoeisel gemeten wordt. Hernoemd op zip-niveau zodat de twee grafieken, het afdrukbereik en de documenteigenschappen mee wijzigden en niets verloren ging.</t>
+        </is>
+      </c>
+      <c r="D55" s="23" t="inlineStr">
+        <is>
+          <t>Pressure monitoring tool_patient.xlsx</t>
+        </is>
+      </c>
+      <c r="E55" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F55" s="23" t="inlineStr">
+        <is>
+          <t>Klaar</t>
+        </is>
+      </c>
+      <c r="G55" s="23" t="inlineStr">
+        <is>
+          <t>14 sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" s="14">
+      <c r="A56" s="26" t="n"/>
+      <c r="B56" s="23" t="inlineStr">
+        <is>
+          <t>Titel van eCRF 24 zegt '(visit 2)'</t>
+        </is>
+      </c>
+      <c r="C56" s="23" t="inlineStr">
+        <is>
+          <t>Het formulier wordt ook op maand 6, 12 en 18 gebruikt, maar de titel noemt alleen visite 2. Nagaan of de titel ruimer moet of dat er per meetmoment een kopie komt.</t>
+        </is>
+      </c>
+      <c r="D56" s="23" t="inlineStr">
+        <is>
+          <t>eCRF 24</t>
+        </is>
+      </c>
+      <c r="E56" s="23" t="inlineStr">
+        <is>
+          <t>Laag</t>
+        </is>
+      </c>
+      <c r="F56" s="23" t="inlineStr">
+        <is>
+          <t>Te doen</t>
+        </is>
+      </c>
+      <c r="G56" s="23" t="inlineStr">
         <is>
           <t>Vastgesteld 14 sep</t>
         </is>
@@ -5919,7 +5985,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F29 F38:F43 F44:F46 F47:F49 F50:F53 F54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F29 F38:F43 F44:F46 F47:F49 F50:F53 F54 F55:F56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Te doen,Bezig,Klaar,Geblokkeerd,Vervalt"</formula1>
     </dataValidation>
   </dataValidations>

--- a/PARADISE_WP1_afvinklijst.xlsx
+++ b/PARADISE_WP1_afvinklijst.xlsx
@@ -4280,8 +4280,8 @@
   <mergeCells count="11">
     <mergeCell ref="A65:I65"/>
     <mergeCell ref="A73:I73"/>
+    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A60:I60"/>
     <mergeCell ref="A1:I1"/>
@@ -5833,12 +5833,12 @@
       <c r="A53" s="26" t="n"/>
       <c r="B53" s="23" t="inlineStr">
         <is>
-          <t>Pressure Monitoring Tool bijwerken</t>
+          <t>Pressure Monitoring Tool: blad Visit naar 8 regio's</t>
         </is>
       </c>
       <c r="C53" s="23" t="inlineStr">
         <is>
-          <t>De tool kent zes regio's per voet in plaats van acht: de middenvoet is niet gesplitst in mediaal en lateraal en tenen 2-5 ontbreken. Dat raakt het samenvattingsblok én de twee blokken RAW DATA EXPORT, en dus ook het masker: dat moet zestien velden opleveren in plaats van twaalf. De kolomtitel 'Barefoot' is enkel een verkeerd label — bedoeld is de meting zonder aangepaste zool.</t>
+          <t>Op 14 september gedaan: opschriften 'Barefoot' vervangen door 'zonder zool' (ook in de vier grafiektitels, die vaste tekst waren), en een blad 'Meting' toegevoegd met wat de clinicus noteert — inclusief de acht regio's met maskercodes A-P. Wat nog moet: het blad 'Visit' van zes naar acht regio's per voet, in het overzicht, in de twee blokken RAW DATA EXPORT én in de hulpkolommen waar de grafieken uit lezen. Pas te doen zodra het masker de zestien velden oplevert.</t>
         </is>
       </c>
       <c r="D53" s="23" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="F53" s="23" t="inlineStr">
         <is>
-          <t>Te doen</t>
+          <t>Bezig</t>
         </is>
       </c>
       <c r="G53" s="23" t="inlineStr">
         <is>
-          <t>Nagekeken 14 sep; 8 regio's bevestigd</t>
+          <t>Deels gedaan 14 sep; rest hangt aan het masker</t>
         </is>
       </c>
     </row>

--- a/PARADISE_WP1_afvinklijst.xlsx
+++ b/PARADISE_WP1_afvinklijst.xlsx
@@ -4279,8 +4279,8 @@
   <autoFilter ref="A4:I79"/>
   <mergeCells count="11">
     <mergeCell ref="A65:I65"/>
+    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A73:I73"/>
-    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A60:I60"/>
@@ -4323,7 +4323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="14" min="1" max="1"/>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C38" s="23" t="inlineStr">
         <is>
-          <t>De database bestaat sinds 14 september onder de naam Sint_Jan_Paradise_Project, met een testpersoon erin. Wat nog niet vastligt: of de klinieken rechtstreeks vanuit de database meten dan wel in novel studio, of er een centrale database komt of een per centrum, en hoe de vijf andere centra erin terechtkomen.</t>
+          <t>Beslist op 14 september: de meting start in de database, niet in novel studio. De clinicus zoekt de deelnemer, maakt het bezoek aan en drukt in het tabblad pedar Files op Measure, zodat het bestand meteen aan persoon en bezoek hangt. Wat nog niet vastligt: één centrale database of één per centrum, hoe de vijf andere centra erin raken, en de back-up.</t>
         </is>
       </c>
       <c r="D38" s="23" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G38" s="23" t="inlineStr">
         <is>
-          <t>Aangemaakt 14 sep; route nog open</t>
+          <t>Meetroute beslist 14 sep; beheer nog open</t>
         </is>
       </c>
     </row>
@@ -5956,6 +5956,72 @@
         </is>
       </c>
       <c r="G56" s="23" t="inlineStr">
+        <is>
+          <t>Vastgesteld 14 sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" s="14">
+      <c r="A57" s="26" t="n"/>
+      <c r="B57" s="23" t="inlineStr">
+        <is>
+          <t>Afsluitprocedure en reset in de SOP</t>
+        </is>
+      </c>
+      <c r="C57" s="23" t="inlineStr">
+        <is>
+          <t>Hoofdstuk 15 beschrijft het afsluiten in volgorde: meting gestopt, novel studio dicht, meting gecontroleerd in de database, bezoek sluiten, zenders uit, zolen opbergen, router uit, laders. Hoofdstuk 16 geeft vijf treden van licht naar zwaar om iets vastgelopens terug te zetten, met de regel dat na elke reset opnieuw nulgesteld wordt en beide condities over moeten.</t>
+        </is>
+      </c>
+      <c r="D57" s="23" t="inlineStr">
+        <is>
+          <t>SOP 09b</t>
+        </is>
+      </c>
+      <c r="E57" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F57" s="23" t="inlineStr">
+        <is>
+          <t>Klaar</t>
+        </is>
+      </c>
+      <c r="G57" s="23" t="inlineStr">
+        <is>
+          <t>14 sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" s="14">
+      <c r="A58" s="26" t="n"/>
+      <c r="B58" s="23" t="inlineStr">
+        <is>
+          <t>Fabrieksreset van de zender opvragen bij novel</t>
+        </is>
+      </c>
+      <c r="C58" s="23" t="inlineStr">
+        <is>
+          <t>In het materiaal dat we in huis hebben staat geen fabrieksreset van de zender beschreven. De SOP waarschuwt nu om er geen uit te proberen, omdat een zender met gewiste configuratiebestanden onbruikbaar is. Opvragen bij novel en als trede 6 toevoegen.</t>
+        </is>
+      </c>
+      <c r="D58" s="23" t="inlineStr">
+        <is>
+          <t>SOP 09b hfst. 16</t>
+        </is>
+      </c>
+      <c r="E58" s="23" t="inlineStr">
+        <is>
+          <t>Middel</t>
+        </is>
+      </c>
+      <c r="F58" s="23" t="inlineStr">
+        <is>
+          <t>Te doen</t>
+        </is>
+      </c>
+      <c r="G58" s="23" t="inlineStr">
         <is>
           <t>Vastgesteld 14 sep</t>
         </is>
@@ -5985,7 +6051,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F29 F38:F43 F44:F46 F47:F49 F50:F53 F54 F55:F56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F29 F38:F43 F44:F46 F47:F49 F50:F53 F54 F55:F56 F57:F58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Te doen,Bezig,Klaar,Geblokkeerd,Vervalt"</formula1>
     </dataValidation>
   </dataValidations>

--- a/PARADISE_WP1_afvinklijst.xlsx
+++ b/PARADISE_WP1_afvinklijst.xlsx
@@ -4279,9 +4279,9 @@
   <autoFilter ref="A4:I79"/>
   <mergeCells count="11">
     <mergeCell ref="A65:I65"/>
-    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A73:I73"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A60:I60"/>
     <mergeCell ref="A1:I1"/>
@@ -4349,7 +4349,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="26.1" customHeight="1" s="14">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -4781,7 +4780,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Ontbreekt volledig; voor MoveMonitor (19b) en Orthotimer (25b) bestaat er wel een</t>
+          <t>Gedaan: eCRF 09b bestaat, 18 hoofdstukken, 55 stappen, 17 figuren. Nog 7 openstaande punten achteraan het document.</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
@@ -4796,12 +4795,12 @@
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>Te doen</t>
+          <t>Klaar</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Toestel waarop de klinische beslissing rust</t>
+          <t>Afgewerkt 14 sep</t>
         </is>
       </c>
     </row>
@@ -4996,7 +4995,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="25" t="inlineStr">
         <is>
@@ -5211,7 +5209,7 @@
       </c>
       <c r="C34" s="23" t="inlineStr">
         <is>
-          <t>Per deelnemer, meetmoment en conditie een plek om het MPP-beeld in te plakken, plus velden voor de drie hoogste waarden met hun plaats</t>
+          <t>Gedaan: het blad 'Meting' van de Pressure Monitoring Tool heeft blok 4 voor de drie hoogste waarden met hun plaats en blok 6 voor de twee schermafbeeldingen, per conditie.</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
@@ -5226,12 +5224,12 @@
       </c>
       <c r="F34" s="23" t="inlineStr">
         <is>
-          <t>Te doen</t>
+          <t>Klaar</t>
         </is>
       </c>
       <c r="G34" s="23" t="inlineStr">
         <is>
-          <t>Volgt uit de beslissing van 11 sep</t>
+          <t>Afgewerkt 14 sep</t>
         </is>
       </c>
     </row>
@@ -5409,7 +5407,7 @@
       </c>
       <c r="C40" s="23" t="inlineStr">
         <is>
-          <t>De database vraagt uit zichzelf naam en geboortedatum. Vastleggen dat er uitsluitend de deelnemerscode in gaat, en dat in de SOP en het datamanagementplan zetten.</t>
+          <t>Beslist en in de SOP verwerkt: deelnemerscode in ID en External ID, X in beide naamvelden, 01/01/1900 als geboortedatum. Rest nog: dit ook in het datamanagementplan zetten.</t>
         </is>
       </c>
       <c r="D40" s="23" t="inlineStr">
@@ -5424,12 +5422,12 @@
       </c>
       <c r="F40" s="23" t="inlineStr">
         <is>
-          <t>Te doen</t>
+          <t>Bezig</t>
         </is>
       </c>
       <c r="G40" s="23" t="inlineStr">
         <is>
-          <t>GDPR</t>
+          <t>Beslist 14 sep; DMP nog</t>
         </is>
       </c>
     </row>
@@ -5475,7 +5473,7 @@
       </c>
       <c r="C42" s="23" t="inlineStr">
         <is>
-          <t>Novel studio bewaart lokaal in C:\Users\Public\Documents\Novel Studio\plidar_data. Vastleggen hoe die bestanden bij het studieteam raken en onder welke naam ze in de database gaan.</t>
+          <t>Deels: de route van de Pressure Monitoring Tool ligt vast (opslaan, mailen naar janou.debuyser@kuleuven.be, lokaal laten staan). Nog open: hoe het geexporteerde pedar-bestand zelf bij het studieteam raakt, en onder welke naam.</t>
         </is>
       </c>
       <c r="D42" s="23" t="inlineStr">
@@ -5490,12 +5488,12 @@
       </c>
       <c r="F42" s="23" t="inlineStr">
         <is>
-          <t>Te doen</t>
+          <t>Bezig</t>
         </is>
       </c>
       <c r="G42" s="23" t="inlineStr">
         <is>
-          <t>Hangt aan de formulierenroute</t>
+          <t>Deels beslist 14 sep</t>
         </is>
       </c>
     </row>

--- a/PARADISE_WP1_afvinklijst.xlsx
+++ b/PARADISE_WP1_afvinklijst.xlsx
@@ -4280,8 +4280,8 @@
   <mergeCells count="11">
     <mergeCell ref="A65:I65"/>
     <mergeCell ref="A73:I73"/>
+    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A60:I60"/>
     <mergeCell ref="A1:I1"/>
@@ -4349,6 +4349,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="26.1" customHeight="1" s="14">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -4445,7 +4446,7 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>De zin over identieke, door elkaar gestoken enveloppen in de methodesectie zetten, en 'variable permuted blocks' uit het onderschrift van figuur 1 halen</t>
+          <t>Gedaan: de methodesectie beschrijft nu hoe de volgorde tot stand komt (SPIRIT 16a) - 24 toewijzingen per centrum, 12 per arm, in identieke ondoorzichtige enveloppen, samen geschud en pas daarna genummerd, geen blokschema - met de voorspelbaarheid tegen het einde van een centrum er eerlijk bij. 'Variable permuted blocks' is uit het onderschrift van figuur 1.</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
@@ -4460,12 +4461,12 @@
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>Te doen</t>
+          <t>Klaar</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>SPIRIT-item 16a; methode beslist 10 sep</t>
+          <t>Afgewerkt 14 sep</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4481,7 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Objectives en Hypotheses formuleren nog een dubbel doel; gelijkzetten met het ene primaire eindpunt</t>
+          <t>Gedaan: Objectives noemt een primair doel (ulcusrecidief over 18 maanden) met therapietrouw als vooraf vastgelegde mediator, primair geanalyseerd op 12 maanden. Hypotheses is teruggebracht tot een hypothese, met de mediator erbij en zonder eigen succescriterium.</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
@@ -4495,10 +4496,14 @@
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>Te doen</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="n"/>
+          <t>Klaar</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Afgewerkt 14 sep</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="25.5" customHeight="1" s="14">
       <c r="A9" s="9" t="n">
@@ -4656,7 +4661,7 @@
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>Markering toevoegen voor figuur 1, 4 en 5; de dubbele markering voor tabel 2 weghalen; bijlage 4 en figuur 5 aanhalen in de tekst</t>
+          <t>Gedaan: markeringen toegevoegd voor figuur 1, 4 en 5; de dubbele markering voor tabel 2 verwijderd. Alle negen figuren en tabellen hebben er nu precies een. Bijlage 4 wordt aangehaald in de statistieksectie en figuur 5 in de exploratieve analyse.</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -4671,10 +4676,14 @@
       </c>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t>Te doen</t>
-        </is>
-      </c>
-      <c r="G14" s="23" t="inlineStr"/>
+          <t>Klaar</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>Afgewerkt 14 sep</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n">
@@ -4718,7 +4727,7 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Drie criteria aanvullen (PEDIS graad 3, immunosuppressie, stabiele vaatstatus) en 'niet de eerste metatarsaalkop' weghalen</t>
+          <t>Gedaan: PEDIS graad 3 en immunosuppressieve therapie toegevoegd bij de exclusie (nu negen), stabiele vaatstatus toegevoegd bij de inclusie (nu zes), en '(niet de eerste metatarsaalkop)' vervangen door 'de eerste inbegrepen'.</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
@@ -4733,10 +4742,14 @@
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>Te doen</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="n"/>
+          <t>Klaar</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Afgewerkt 14 sep</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="n">
@@ -4940,7 +4953,7 @@
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>De ICC-drempel verplaatsen naar het klinische toestel, en de methodevergelijking uit de startvoorwaarden halen</t>
+          <t>Gedaan: de ICC-drempel van 0,80 staat nu op de Novel pedar in plaats van de F-Scan GO, en de methodevergelijking is geen startvoorwaarde meer maar loopt parallel aan de trial. Van zeven Go-criteria blijven er zes over.</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
@@ -4955,10 +4968,14 @@
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>Te doen</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="n"/>
+          <t>Klaar</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>Afgewerkt 14 sep</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="9" t="n">
@@ -4995,6 +5012,7 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="25" t="inlineStr">
         <is>
@@ -5044,7 +5062,7 @@
       </c>
       <c r="C29" s="23" t="inlineStr">
         <is>
-          <t>Beschrijft nu een blootsvoetse baselinemeting met sensoren op de voet; moet in-shoe zónder de CMFO worden</t>
+          <t>Gedaan: de inleiding beschrijft nu een in-shoe meting zonder de CMFO, in het schoeisel waarmee de deelnemer binnenkomt; beide voeten tegelijk opgenomen en per voet uitgelezen. De titel van tabel 1 zegt 'in het schoeisel zonder diabetische CMFO'. De acht regio's stonden er al goed in.</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
@@ -5059,12 +5077,12 @@
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t>Te doen</t>
+          <t>Klaar</t>
         </is>
       </c>
       <c r="G29" s="23" t="inlineStr">
         <is>
-          <t>Volgt uit de beslissing</t>
+          <t>Afgewerkt 14 sep</t>
         </is>
       </c>
     </row>

--- a/PARADISE_WP1_afvinklijst.xlsx
+++ b/PARADISE_WP1_afvinklijst.xlsx
@@ -4279,8 +4279,8 @@
   <autoFilter ref="A4:I79"/>
   <mergeCells count="11">
     <mergeCell ref="A65:I65"/>
+    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A73:I73"/>
-    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A60:I60"/>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Kiezen tussen een onafhankelijke geblindeerde commissie en het multidisciplinaire team dat nu in de methodesectie staat, en dan zes plaatsen gelijkzetten</t>
+          <t>Beslist: het multidisciplinaire team, zoals de diagnose in de praktijk gesteld wordt. Er komt geen onafhankelijke geblindeerde adjudicatiecommissie. Zes plaatsen gelijkgezet: methodesectie (stond al goed), Strengths, Limitations, tabel 2 en de statistieksectie. In de Limitations staat het ontbreken van geblindeerde adjudicatie nu zelf als beperking.</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
@@ -4426,12 +4426,12 @@
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>Te doen</t>
+          <t>Klaar</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Eerst doen: raakt ook de werving</t>
+          <t>Beslissing PI 14 sep</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Kiezen tussen een onafhankelijke geblindeerde commissie en het multidisciplinaire team dat nu in de methodesectie staat, en dan zes plaatsen gelijkzetten</t>
+          <t>Beslist: het multidisciplinaire team, zoals de diagnose in de praktijk gesteld wordt. Er komt geen onafhankelijke geblindeerde adjudicatiecommissie. Zes plaatsen gelijkgezet: methodesectie (stond al goed), Strengths, Limitations, tabel 2 en de statistieksectie. In de Limitations staat het ontbreken van geblindeerde adjudicatie nu zelf als beperking.</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>Te doen</t>
+          <t>Klaar</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>Eerst doen: raakt ook de werving</t>
+          <t>Beslissing PI 14 sep</t>
         </is>
       </c>
     </row>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>'Academic staff' preciseren: wie voert in, en welke rollen krijgt de databank</t>
+          <t>Beslist: een centrale REDCap-databank. De centra vullen papieren bronformulieren in en het studieteam zet die centraal over; sitepersoneel voert zelf niets in en het papieren werkblad blijft als brondocument op de site. 'Academic staff' is uit het manuscript.</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
@@ -4889,10 +4889,14 @@
       </c>
       <c r="F21" s="10" t="inlineStr">
         <is>
-          <t>Te doen</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="n"/>
+          <t>Klaar</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>Beslissing PI 14 sep</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="25.5" customHeight="1" s="14">
       <c r="A22" s="9" t="n">
@@ -5293,7 +5297,7 @@
       </c>
       <c r="C36" s="23" t="inlineStr">
         <is>
-          <t>MVP O telt alle frames mee, MVP LF alleen geladen frames, MVP LC ook zonder nulsensoren. Voor de norm maakt het niet uit: die gaat op MPP</t>
+          <t>Vervalt: de MVP-weergave is niet van belang voor de studie. De norm gaat op MPP.</t>
         </is>
       </c>
       <c r="D36" s="23" t="inlineStr">
@@ -5308,12 +5312,12 @@
       </c>
       <c r="F36" s="23" t="inlineStr">
         <is>
-          <t>Te doen</t>
+          <t>Vervalt</t>
         </is>
       </c>
       <c r="G36" s="23" t="inlineStr">
         <is>
-          <t>Openstaand punt 28</t>
+          <t>Beslissing PI 14 sep</t>
         </is>
       </c>
     </row>
@@ -5359,7 +5363,7 @@
       </c>
       <c r="C38" s="23" t="inlineStr">
         <is>
-          <t>Beslist op 14 september: de meting start in de database, niet in novel studio. De clinicus zoekt de deelnemer, maakt het bezoek aan en drukt in het tabblad pedar Files op Measure, zodat het bestand meteen aan persoon en bezoek hangt. Wat nog niet vastligt: één centrale database of één per centrum, hoe de vijf andere centra erin raken, en de back-up.</t>
+          <t>De meting start in de novel database (14 sep). De studiedatabank is beslist: één centrale REDCap, centraal ingevoerd vanaf papier. Voor de novel database zelf blijft open of elk centrum een lokale krijgt en hoe de metingen samenkomen.</t>
         </is>
       </c>
       <c r="D38" s="23" t="inlineStr">
@@ -5379,7 +5383,7 @@
       </c>
       <c r="G38" s="23" t="inlineStr">
         <is>
-          <t>Meetroute beslist 14 sep; beheer nog open</t>
+          <t>REDCap beslist 14 sep; novel-archief nog open</t>
         </is>
       </c>
     </row>

--- a/PARADISE_WP1_afvinklijst.xlsx
+++ b/PARADISE_WP1_afvinklijst.xlsx
@@ -4279,9 +4279,9 @@
   <autoFilter ref="A4:I79"/>
   <mergeCells count="11">
     <mergeCell ref="A65:I65"/>
-    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A73:I73"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A41:I41"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A60:I60"/>
     <mergeCell ref="A1:I1"/>
@@ -4323,7 +4323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="14" min="1" max="1"/>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>De drukmeting aanvinken op V2 in tabel 2, en de aparte visite 0 uit het protocol expliciet maken</t>
+          <t>Gedaan: de drukmeting is aangevinkt op V2 in tabel 2 van het manuscript. De aparte visite 0 in het protocoldocument is NIET gedaan: dat vraagt een extra kolom in het SPIRIT-schema en een ingreep in Protocol_PARADISE_17_05_2026.docx.</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -4566,10 +4566,14 @@
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>Te doen</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="n"/>
+          <t>Bezig</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>V2 gedaan 14 sep; visite 0 nog</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="38.25" customHeight="1" s="14">
       <c r="A11" s="9" t="n">
@@ -4909,7 +4913,7 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Registratienummer en -datum, startdatum rekrutering, herschrijfmarkering ethiek, belangenconflicten, auteursbijdragen, dankwoord</t>
+          <t>Drie ingevuld: belangenconflicten, auteursbijdragen (CRediT, door de auteurs te bevestigen) en dankwoord. Vier blijven open omdat ze informatie van buiten vragen: registratienummer en -datum bij ClinicalTrials.gov, de startdatum van de rekrutering en de herschrijfmarkering bij de ethiekgoedkeuring.</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
@@ -4924,12 +4928,12 @@
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>Te doen</t>
+          <t>Bezig</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Zie blad Manuscriptpakket</t>
+          <t>3 van 7 gedaan 14 sep</t>
         </is>
       </c>
     </row>
@@ -5891,7 +5895,7 @@
       </c>
       <c r="C54" s="23" t="inlineStr">
         <is>
-          <t>De doelregio's zijn per voet de twee plaatsen in de voorvoet of middenvoet met de hoogste piekdruk boven 200 kPa — de hiel telt niet mee. En de zool wordt ook aangepast als de piekdruk op een doelregio met 5% of meer gestegen is tegenover de vorige keer. Nagaan of die twee ook in het protocol en de SAP horen.</t>
+          <t>Gedaan, en het bleek meer dan dat: de methodesectie noemde het ontlastingscriterium helemaal niet - 200 kPa en de 25% stonden alleen in de inleiding als beschrijving van de literatuur. Nu staan in de methodesectie de drie doelregio's (vorige ulcusplaats plus de twee voorvoet- of middenvoetregio's boven 200 kPa, hiel niet), de norm met de vergelijking zonder zool in dezelfde sessie, en de 5%-stijgingsregel bij opvolging.</t>
         </is>
       </c>
       <c r="D54" s="23" t="inlineStr">
@@ -5906,12 +5910,12 @@
       </c>
       <c r="F54" s="23" t="inlineStr">
         <is>
-          <t>Te doen</t>
+          <t>Klaar</t>
         </is>
       </c>
       <c r="G54" s="23" t="inlineStr">
         <is>
-          <t>Vastgesteld 14 sep</t>
+          <t>Afgewerkt 14 sep</t>
         </is>
       </c>
     </row>
@@ -5957,7 +5961,7 @@
       </c>
       <c r="C56" s="23" t="inlineStr">
         <is>
-          <t>Het formulier wordt ook op maand 6, 12 en 18 gebruikt, maar de titel noemt alleen visite 2. Nagaan of de titel ruimer moet of dat er per meetmoment een kopie komt.</t>
+          <t>Gedaan: de titel zegt nu '(visit 2, and months 6, 12 and 18)'.</t>
         </is>
       </c>
       <c r="D56" s="23" t="inlineStr">
@@ -5972,12 +5976,12 @@
       </c>
       <c r="F56" s="23" t="inlineStr">
         <is>
-          <t>Te doen</t>
+          <t>Klaar</t>
         </is>
       </c>
       <c r="G56" s="23" t="inlineStr">
         <is>
-          <t>Vastgesteld 14 sep</t>
+          <t>Afgewerkt 14 sep</t>
         </is>
       </c>
     </row>
@@ -6044,6 +6048,39 @@
       <c r="G58" s="23" t="inlineStr">
         <is>
           <t>Vastgesteld 14 sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" s="14">
+      <c r="A59" s="26" t="n"/>
+      <c r="B59" s="23" t="inlineStr">
+        <is>
+          <t>Alinea 65 zei 'own baseline pressure'</t>
+        </is>
+      </c>
+      <c r="C59" s="23" t="inlineStr">
+        <is>
+          <t>Gevonden bij het invoegen van het ontlastingscriterium: de sectie Tailoring and fidelity zei dat het ontlastingsdoel tegen de eigen baselinedruk ligt. Rechtgezet naar de meting zonder de zool in dezelfde sessie, conform de beslissing van 11 september.</t>
+        </is>
+      </c>
+      <c r="D59" s="23" t="inlineStr">
+        <is>
+          <t>Manuscript</t>
+        </is>
+      </c>
+      <c r="E59" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F59" s="23" t="inlineStr">
+        <is>
+          <t>Klaar</t>
+        </is>
+      </c>
+      <c r="G59" s="23" t="inlineStr">
+        <is>
+          <t>Rechtgezet 14 sep</t>
         </is>
       </c>
     </row>
@@ -6071,7 +6108,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F5:F29 F38:F43 F44:F46 F47:F49 F50:F53 F54 F55:F56 F57:F58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:F29 F38:F43 F44:F46 F47:F49 F50:F53 F54 F55:F56 F57:F58 F59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Te doen,Bezig,Klaar,Geblokkeerd,Vervalt"</formula1>
     </dataValidation>
   </dataValidations>

--- a/PARADISE_WP1_afvinklijst.xlsx
+++ b/PARADISE_WP1_afvinklijst.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kuleuven-my.sharepoint.com/personal/janou_debuyser_kuleuven_be1/Documents/Documents/PhD Brugge/Site/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_BD600FB87C3722EDD7AEB33573C921E60A419D9F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1C99987-CE0B-420D-A46A-FA8DD4A5D6B8}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_BD600FB87C3722EDD7AEB33573C921E60A419D9F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55FD3096-EDF3-474D-A7E7-6F8E15AADC44}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overzicht" sheetId="1" r:id="rId1"/>
@@ -1813,16 +1813,16 @@
     <t>Novel Pedar, database en software aanwezig</t>
   </si>
   <si>
-    <t>Pedar als klinisch toestel met trublu-kalibratie; F-Scan GO alleen studieteam; acht regio's; alles in-shoe, zónder én mét de zool gemeten; norm &lt; 200 kPa mét de zool óf ≥ 25% lager dan zonder de zool op visite 2 (vaste referentie, ook op maand 6, 12 en 18); behaalde reductie als fidelity-maat</t>
-  </si>
-  <si>
-    <t>Alles in-shoe, twee condities: zónder en mét de CMFO. De 25%-reductie rekent tegenover de meting zonder zool op visite 2, die ook op maand 6, 12 en 18 de referentie blijft (gepreciseerd op 22 september). Tabel 4 van het manuscript had het goed</t>
-  </si>
-  <si>
     <t>Gedaan, en het bleek meer dan dat: de methodesectie noemde het ontlastingscriterium helemaal niet - 200 kPa en de 25% stonden alleen in de inleiding als beschrijving van de literatuur. Nu staan in de methodesectie de drie doelregio's (vorige ulcusplaats plus de twee voorvoet- of middenvoetregio's boven 200 kPa, hiel niet), de norm met de vergelijking met de meting zonder zool op visite 2 (op 25 september ook zo in het manuscript gezet), en de 5%-stijgingsregel bij opvolging.</t>
   </si>
   <si>
     <t>Gevonden bij het invoegen van het ontlastingscriterium: de sectie Tailoring and fidelity zei dat het ontlastingsdoel tegen de eigen baselinedruk ligt. Rechtgezet naar de meting zonder de zool, conform de beslissing van 11 september; op 22 september gepreciseerd tot de meting zonder zool op visite 2.</t>
+  </si>
+  <si>
+    <t>Pedar als klinisch toestel met trublu-kalibratie; F-Scan GO alleen studieteam; acht regio's; alles in-shoe, zónder én mét de zool gemeten; norm &lt; 200 kPa mét de zool óf ≥ 25% lager dan zonder de zool in dezelfde sessie, tot drie aanpassingen; behaalde reductie als fidelity-maat</t>
+  </si>
+  <si>
+    <t>Alles in-shoe, twee condities: zónder en mét de CMFO. De 25%-reductie rekent tegenover de meting zonder zool in dezelfde sessie, tot drie aanpassingen (beslissing 6 oktober; de vaste referentie van 22 september vervalt). Tabel 4 van het manuscript had het goed</t>
   </si>
 </sst>
 </file>
@@ -2537,7 +2537,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="5" width="10" customWidth="1"/>
@@ -2546,15 +2546,15 @@
     <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="22"/>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -2562,7 +2562,7 @@
       <c r="E4" s="20"/>
       <c r="F4" s="20"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>38</v>
       </c>
@@ -2588,7 +2588,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>45</v>
       </c>
@@ -2621,7 +2621,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>46</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>47</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>0</v>
       </c>
@@ -2720,7 +2720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>48</v>
       </c>
@@ -2753,12 +2753,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
     </row>
   </sheetData>
@@ -2775,7 +2775,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I79"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -2788,7 +2788,7 @@
     <col min="9" max="9" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="21" t="s">
         <v>50</v>
       </c>
@@ -2801,7 +2801,7 @@
       <c r="H1" s="20"/>
       <c r="I1" s="20"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="19" t="s">
         <v>51</v>
       </c>
@@ -2814,7 +2814,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="4" spans="1:9" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
         <v>52</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="23" t="s">
         <v>59</v>
       </c>
@@ -2856,7 +2856,7 @@
       <c r="H5" s="24"/>
       <c r="I5" s="25"/>
     </row>
-    <row r="6" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
         <v>60</v>
       </c>
@@ -2885,7 +2885,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>68</v>
       </c>
@@ -2914,7 +2914,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>73</v>
       </c>
@@ -2943,7 +2943,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>78</v>
       </c>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="I9" s="10"/>
     </row>
-    <row r="10" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>83</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
         <v>88</v>
       </c>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="I11" s="10"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
         <v>94</v>
       </c>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="I12" s="10"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
         <v>98</v>
       </c>
@@ -3080,7 +3080,7 @@
       </c>
       <c r="I13" s="10"/>
     </row>
-    <row r="14" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
         <v>102</v>
       </c>
@@ -3109,7 +3109,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
         <v>108</v>
       </c>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="I15" s="10"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
         <v>114</v>
       </c>
@@ -3165,7 +3165,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="23" t="s">
         <v>118</v>
       </c>
@@ -3178,7 +3178,7 @@
       <c r="H17" s="24"/>
       <c r="I17" s="25"/>
     </row>
-    <row r="18" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
         <v>119</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
         <v>124</v>
       </c>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="I19" s="10"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
         <v>130</v>
       </c>
@@ -3263,7 +3263,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
         <v>134</v>
       </c>
@@ -3290,7 +3290,7 @@
       </c>
       <c r="I21" s="10"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
         <v>137</v>
       </c>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="I22" s="10"/>
     </row>
-    <row r="23" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
         <v>140</v>
       </c>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="I23" s="10"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
         <v>143</v>
       </c>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="I24" s="10"/>
     </row>
-    <row r="25" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
         <v>149</v>
       </c>
@@ -3400,7 +3400,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="23" t="s">
         <v>154</v>
       </c>
@@ -3413,7 +3413,7 @@
       <c r="H26" s="24"/>
       <c r="I26" s="25"/>
     </row>
-    <row r="27" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
         <v>155</v>
       </c>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="I27" s="10"/>
     </row>
-    <row r="28" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
         <v>160</v>
       </c>
@@ -3448,7 +3448,7 @@
         <v>161</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D28" s="10" t="s">
         <v>111</v>
@@ -3469,7 +3469,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
         <v>164</v>
       </c>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="I29" s="10"/>
     </row>
-    <row r="30" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
         <v>168</v>
       </c>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="I30" s="10"/>
     </row>
-    <row r="31" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
         <v>174</v>
       </c>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="I31" s="10"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
         <v>178</v>
       </c>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="I32" s="10"/>
     </row>
-    <row r="33" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
         <v>183</v>
       </c>
@@ -3606,7 +3606,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
         <v>188</v>
       </c>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="I34" s="10"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="23" t="s">
         <v>193</v>
       </c>
@@ -3646,7 +3646,7 @@
       <c r="H35" s="24"/>
       <c r="I35" s="25"/>
     </row>
-    <row r="36" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
         <v>194</v>
       </c>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="I36" s="10"/>
     </row>
-    <row r="37" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
         <v>198</v>
       </c>
@@ -3702,7 +3702,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
         <v>202</v>
       </c>
@@ -3731,7 +3731,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
         <v>207</v>
       </c>
@@ -3760,7 +3760,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
         <v>212</v>
       </c>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="I40" s="10"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="23" t="s">
         <v>215</v>
       </c>
@@ -3800,7 +3800,7 @@
       <c r="H41" s="24"/>
       <c r="I41" s="25"/>
     </row>
-    <row r="42" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
         <v>216</v>
       </c>
@@ -3829,7 +3829,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
         <v>222</v>
       </c>
@@ -3858,7 +3858,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
         <v>226</v>
       </c>
@@ -3887,7 +3887,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
         <v>230</v>
       </c>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="I45" s="10"/>
     </row>
-    <row r="46" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
         <v>235</v>
       </c>
@@ -3943,7 +3943,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
         <v>241</v>
       </c>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="I47" s="10"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
         <v>244</v>
       </c>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="I48" s="10"/>
     </row>
-    <row r="49" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="9" t="s">
         <v>247</v>
       </c>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="I49" s="10"/>
     </row>
-    <row r="50" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="9" t="s">
         <v>250</v>
       </c>
@@ -4053,7 +4053,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" s="9" t="s">
         <v>255</v>
       </c>
@@ -4082,7 +4082,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="9" t="s">
         <v>260</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" s="23" t="s">
         <v>266</v>
       </c>
@@ -4124,7 +4124,7 @@
       <c r="H53" s="24"/>
       <c r="I53" s="25"/>
     </row>
-    <row r="54" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="9" t="s">
         <v>267</v>
       </c>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="I54" s="10"/>
     </row>
-    <row r="55" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="9" t="s">
         <v>272</v>
       </c>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="I55" s="10"/>
     </row>
-    <row r="56" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="9" t="s">
         <v>275</v>
       </c>
@@ -4207,7 +4207,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="9" t="s">
         <v>282</v>
       </c>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="I57" s="10"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" s="9" t="s">
         <v>287</v>
       </c>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="I58" s="10"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" s="9" t="s">
         <v>290</v>
       </c>
@@ -4290,7 +4290,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" s="23" t="s">
         <v>295</v>
       </c>
@@ -4303,7 +4303,7 @@
       <c r="H60" s="24"/>
       <c r="I60" s="25"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" s="9" t="s">
         <v>296</v>
       </c>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="I61" s="10"/>
     </row>
-    <row r="62" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="9" t="s">
         <v>300</v>
       </c>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="I62" s="10"/>
     </row>
-    <row r="63" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="9" t="s">
         <v>305</v>
       </c>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="I63" s="10"/>
     </row>
-    <row r="64" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="9" t="s">
         <v>308</v>
       </c>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="I64" s="10"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" s="23" t="s">
         <v>311</v>
       </c>
@@ -4424,7 +4424,7 @@
       <c r="H65" s="24"/>
       <c r="I65" s="25"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" s="9" t="s">
         <v>312</v>
       </c>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="I66" s="10"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" s="9" t="s">
         <v>319</v>
       </c>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="I67" s="10"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" s="9" t="s">
         <v>323</v>
       </c>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="I68" s="10"/>
     </row>
-    <row r="69" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="9" t="s">
         <v>327</v>
       </c>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="I69" s="10"/>
     </row>
-    <row r="70" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="9" t="s">
         <v>330</v>
       </c>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="I70" s="10"/>
     </row>
-    <row r="71" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="9" t="s">
         <v>333</v>
       </c>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="I71" s="10"/>
     </row>
-    <row r="72" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="9" t="s">
         <v>337</v>
       </c>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="I72" s="10"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" s="23" t="s">
         <v>341</v>
       </c>
@@ -4626,7 +4626,7 @@
       <c r="H73" s="24"/>
       <c r="I73" s="25"/>
     </row>
-    <row r="74" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="9" t="s">
         <v>342</v>
       </c>
@@ -4655,7 +4655,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" s="9" t="s">
         <v>347</v>
       </c>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="I75" s="10"/>
     </row>
-    <row r="76" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="9" t="s">
         <v>353</v>
       </c>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="I76" s="10"/>
     </row>
-    <row r="77" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="9" t="s">
         <v>359</v>
       </c>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="I77" s="10"/>
     </row>
-    <row r="78" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="9" t="s">
         <v>362</v>
       </c>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="I78" s="10"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" s="9" t="s">
         <v>367</v>
       </c>
@@ -4793,17 +4793,17 @@
   </sheetData>
   <autoFilter ref="A4:I79" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="11">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A53:I53"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A26:I26"/>
     <mergeCell ref="A65:I65"/>
     <mergeCell ref="A73:I73"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A41:I41"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="A60:I60"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A17:I17"/>
+    <mergeCell ref="A53:I53"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A26:I26"/>
   </mergeCells>
   <conditionalFormatting sqref="H5:H79">
     <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
@@ -4838,7 +4838,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G59"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -4849,7 +4849,7 @@
     <col min="7" max="7" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="21" t="s">
         <v>46</v>
       </c>
@@ -4860,7 +4860,7 @@
       <c r="F1" s="20"/>
       <c r="G1" s="20"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="19" t="s">
         <v>372</v>
       </c>
@@ -4871,7 +4871,7 @@
       <c r="F2" s="20"/>
       <c r="G2" s="20"/>
     </row>
-    <row r="4" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
         <v>52</v>
       </c>
@@ -4894,7 +4894,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="23" t="s">
         <v>376</v>
       </c>
@@ -4905,7 +4905,7 @@
       <c r="F5" s="24"/>
       <c r="G5" s="25"/>
     </row>
-    <row r="6" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9">
         <v>1</v>
       </c>
@@ -4928,7 +4928,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9">
         <v>2</v>
       </c>
@@ -4951,7 +4951,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="9">
         <v>3</v>
       </c>
@@ -4974,7 +4974,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9">
         <v>4</v>
       </c>
@@ -4997,7 +4997,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9">
         <v>5</v>
       </c>
@@ -5020,7 +5020,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9">
         <v>6</v>
       </c>
@@ -5043,7 +5043,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="23" t="s">
         <v>397</v>
       </c>
@@ -5054,7 +5054,7 @@
       <c r="F12" s="24"/>
       <c r="G12" s="25"/>
     </row>
-    <row r="13" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9">
         <v>7</v>
       </c>
@@ -5075,7 +5075,7 @@
       </c>
       <c r="G13" s="10"/>
     </row>
-    <row r="14" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="16">
         <v>8</v>
       </c>
@@ -5098,7 +5098,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="9">
         <v>9</v>
       </c>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G15" s="10"/>
     </row>
-    <row r="16" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9">
         <v>10</v>
       </c>
@@ -5142,7 +5142,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="9">
         <v>11</v>
       </c>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="G17" s="10"/>
     </row>
-    <row r="18" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9">
         <v>12</v>
       </c>
@@ -5186,7 +5186,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="9">
         <v>13</v>
       </c>
@@ -5197,7 +5197,7 @@
       <c r="F19" s="14"/>
       <c r="G19" s="15"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="9">
         <v>14</v>
       </c>
@@ -5220,7 +5220,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="39" x14ac:dyDescent="0.35">
       <c r="A21" s="9">
         <v>15</v>
       </c>
@@ -5243,7 +5243,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9">
         <v>16</v>
       </c>
@@ -5266,7 +5266,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="23" t="s">
         <v>425</v>
       </c>
@@ -5277,7 +5277,7 @@
       <c r="F23" s="24"/>
       <c r="G23" s="25"/>
     </row>
-    <row r="24" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9">
         <v>17</v>
       </c>
@@ -5300,7 +5300,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="9">
         <v>18</v>
       </c>
@@ -5323,18 +5323,18 @@
         <v>431</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="18" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="39" x14ac:dyDescent="0.35">
       <c r="A28" s="16"/>
       <c r="B28" s="17" t="s">
         <v>433</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="D28" s="17" t="s">
         <v>434</v>
@@ -5349,7 +5349,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="52" x14ac:dyDescent="0.35">
       <c r="A29" s="16"/>
       <c r="B29" s="17" t="s">
         <v>436</v>
@@ -5370,7 +5370,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="39" x14ac:dyDescent="0.35">
       <c r="A30" s="16"/>
       <c r="B30" s="17" t="s">
         <v>439</v>
@@ -5391,7 +5391,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="26" x14ac:dyDescent="0.35">
       <c r="A31" s="16"/>
       <c r="B31" s="17" t="s">
         <v>443</v>
@@ -5412,7 +5412,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="26" x14ac:dyDescent="0.35">
       <c r="A32" s="16"/>
       <c r="B32" s="17" t="s">
         <v>447</v>
@@ -5433,7 +5433,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="26" x14ac:dyDescent="0.35">
       <c r="A33" s="16"/>
       <c r="B33" s="17" t="s">
         <v>451</v>
@@ -5454,7 +5454,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="26" x14ac:dyDescent="0.35">
       <c r="A34" s="16"/>
       <c r="B34" s="17" t="s">
         <v>455</v>
@@ -5475,7 +5475,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="39" x14ac:dyDescent="0.35">
       <c r="A35" s="16"/>
       <c r="B35" s="17" t="s">
         <v>458</v>
@@ -5496,7 +5496,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="26" x14ac:dyDescent="0.35">
       <c r="A36" s="16"/>
       <c r="B36" s="17" t="s">
         <v>461</v>
@@ -5517,7 +5517,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="26" x14ac:dyDescent="0.35">
       <c r="A37" s="16"/>
       <c r="B37" s="17" t="s">
         <v>464</v>
@@ -5538,7 +5538,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="39" x14ac:dyDescent="0.35">
       <c r="A38" s="16"/>
       <c r="B38" s="17" t="s">
         <v>468</v>
@@ -5559,7 +5559,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="52" x14ac:dyDescent="0.35">
       <c r="A39" s="16"/>
       <c r="B39" s="17" t="s">
         <v>472</v>
@@ -5580,7 +5580,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="26" x14ac:dyDescent="0.35">
       <c r="A40" s="16"/>
       <c r="B40" s="17" t="s">
         <v>475</v>
@@ -5601,7 +5601,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="39" x14ac:dyDescent="0.35">
       <c r="A41" s="16"/>
       <c r="B41" s="17" t="s">
         <v>479</v>
@@ -5622,7 +5622,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="39" x14ac:dyDescent="0.35">
       <c r="A42" s="16"/>
       <c r="B42" s="17" t="s">
         <v>482</v>
@@ -5643,7 +5643,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="39" x14ac:dyDescent="0.35">
       <c r="A43" s="16"/>
       <c r="B43" s="17" t="s">
         <v>486</v>
@@ -5664,7 +5664,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="26" x14ac:dyDescent="0.35">
       <c r="A44" s="16"/>
       <c r="B44" s="17" t="s">
         <v>489</v>
@@ -5685,7 +5685,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="26" x14ac:dyDescent="0.35">
       <c r="A45" s="16"/>
       <c r="B45" s="17" t="s">
         <v>491</v>
@@ -5706,7 +5706,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="39" x14ac:dyDescent="0.35">
       <c r="A46" s="16"/>
       <c r="B46" s="17" t="s">
         <v>494</v>
@@ -5727,7 +5727,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="39" x14ac:dyDescent="0.35">
       <c r="A47" s="16"/>
       <c r="B47" s="17" t="s">
         <v>497</v>
@@ -5748,7 +5748,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="26" x14ac:dyDescent="0.35">
       <c r="A48" s="16"/>
       <c r="B48" s="17" t="s">
         <v>499</v>
@@ -5769,7 +5769,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="39" x14ac:dyDescent="0.35">
       <c r="A49" s="16"/>
       <c r="B49" s="17" t="s">
         <v>503</v>
@@ -5790,7 +5790,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="26" x14ac:dyDescent="0.35">
       <c r="A50" s="16"/>
       <c r="B50" s="17" t="s">
         <v>506</v>
@@ -5811,7 +5811,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="39" x14ac:dyDescent="0.35">
       <c r="A51" s="16"/>
       <c r="B51" s="17" t="s">
         <v>508</v>
@@ -5832,7 +5832,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="16"/>
       <c r="B52" s="17" t="s">
         <v>511</v>
@@ -5853,7 +5853,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="78" x14ac:dyDescent="0.35">
       <c r="A53" s="16"/>
       <c r="B53" s="17" t="s">
         <v>514</v>
@@ -5874,13 +5874,13 @@
         <v>517</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="78" x14ac:dyDescent="0.35">
       <c r="A54" s="16"/>
       <c r="B54" s="17" t="s">
         <v>518</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D54" s="17" t="s">
         <v>519</v>
@@ -5895,7 +5895,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="39" x14ac:dyDescent="0.35">
       <c r="A55" s="16"/>
       <c r="B55" s="17" t="s">
         <v>520</v>
@@ -5916,7 +5916,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="16"/>
       <c r="B56" s="17" t="s">
         <v>522</v>
@@ -5937,7 +5937,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="52" x14ac:dyDescent="0.35">
       <c r="A57" s="16"/>
       <c r="B57" s="17" t="s">
         <v>524</v>
@@ -5958,7 +5958,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" ht="39" x14ac:dyDescent="0.35">
       <c r="A58" s="16"/>
       <c r="B58" s="17" t="s">
         <v>526</v>
@@ -5979,13 +5979,13 @@
         <v>529</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" ht="52" x14ac:dyDescent="0.35">
       <c r="A59" s="16"/>
       <c r="B59" s="17" t="s">
         <v>530</v>
       </c>
       <c r="C59" s="17" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D59" s="17" t="s">
         <v>531</v>
@@ -6039,7 +6039,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="52" customWidth="1"/>
@@ -6051,7 +6051,7 @@
     <col min="11" max="11" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="21" t="s">
         <v>533</v>
       </c>
@@ -6061,7 +6061,7 @@
       <c r="E1" s="20"/>
       <c r="F1" s="20"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="19" t="s">
         <v>534</v>
       </c>
@@ -6071,7 +6071,7 @@
       <c r="E2" s="20"/>
       <c r="F2" s="20"/>
     </row>
-    <row r="4" spans="1:11" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
         <v>52</v>
       </c>
@@ -6091,7 +6091,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="23" t="s">
         <v>538</v>
       </c>
@@ -6101,7 +6101,7 @@
       <c r="E5" s="24"/>
       <c r="F5" s="25"/>
     </row>
-    <row r="6" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9">
         <v>1</v>
       </c>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="F6" s="10"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="9">
         <v>2</v>
       </c>
@@ -6139,7 +6139,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="9">
         <v>3</v>
       </c>
@@ -6157,7 +6157,7 @@
       </c>
       <c r="F8" s="10"/>
     </row>
-    <row r="9" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9">
         <v>4</v>
       </c>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="F9" s="10"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="9">
         <v>5</v>
       </c>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="F10" s="10"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="9">
         <v>6</v>
       </c>
@@ -6213,7 +6213,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
         <v>7</v>
       </c>
@@ -6233,12 +6233,12 @@
         <v>561</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>52</v>
       </c>
@@ -6273,7 +6273,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="9">
         <v>1</v>
       </c>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="K16" s="9"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="9">
         <v>2</v>
       </c>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="K17" s="9"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="9">
         <v>3</v>
       </c>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="K18" s="9"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="9">
         <v>4</v>
       </c>
@@ -6357,7 +6357,7 @@
       </c>
       <c r="K19" s="9"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="9">
         <v>5</v>
       </c>
@@ -6378,7 +6378,7 @@
       </c>
       <c r="K20" s="9"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="9">
         <v>6</v>
       </c>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="K21" s="9"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="9">
         <v>7</v>
       </c>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="K22" s="9"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="9">
         <v>8</v>
       </c>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="K23" s="9"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="9">
         <v>9</v>
       </c>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="K24" s="9"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="12">
         <v>10</v>
       </c>
@@ -6527,7 +6527,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
@@ -6537,7 +6537,7 @@
     <col min="7" max="7" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -6548,7 +6548,7 @@
       <c r="F1" s="20"/>
       <c r="G1" s="20"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
@@ -6559,7 +6559,7 @@
       <c r="F2" s="20"/>
       <c r="G2" s="20"/>
     </row>
-    <row r="4" spans="1:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="26.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
@@ -6582,7 +6582,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
         <v>9</v>
       </c>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="G5" s="10"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
         <v>15</v>
       </c>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="G6" s="10"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>18</v>
       </c>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="G7" s="10"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>21</v>
       </c>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="G8" s="10"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>26</v>
       </c>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="G9" s="10"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>31</v>
       </c>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="G10" s="10"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
         <v>33</v>
       </c>
